--- a/Plantilla_Importacion_Vehiculos.xlsx
+++ b/Plantilla_Importacion_Vehiculos.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATOS" sheetId="1" r:id="R832cbeda1a6b4c04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" r:id="R7d721bc1dc2643ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" r:id="R037f9cf0b89545ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATOS" sheetId="1" r:id="Reb26ec98322845f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" r:id="Rce28a400d9c546b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" r:id="R316e7b4a39294e00"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -66,7 +66,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -127,6 +127,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -177,9 +178,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -291,7 +292,7 @@
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
   </x:cols>
@@ -319,15 +320,18 @@
         <x:v>VIN</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>KILOMETRAJE</x:v>
+        <x:v>KM_ACTUAL</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
+        <x:v>PROXIMA_MANTENCION_KM</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
         <x:v>ESTADO</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="K1" s="6" t="str">
         <x:v>QR_CODIGO</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="L1" t="str">
         <x:v>PROXIMA_MANTENCION</x:v>
       </x:c>
     </x:row>
@@ -356,11 +360,14 @@
       <x:c r="H2" s="12" t="n">
         <x:v>15200</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="12" t="n">
+        <x:v>25200</x:v>
+      </x:c>
+      <x:c r="J2" s="12" t="str">
         <x:v>Disponible</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str"/>
-      <x:c r="K2" s="14" t="str">
+      <x:c r="K2" s="14"/>
+      <x:c r="L2" t="str">
         <x:v>2026-12-15</x:v>
       </x:c>
     </x:row>
@@ -376,6 +383,7 @@
       <x:c r="I3" s="12"/>
       <x:c r="J3" s="12"/>
       <x:c r="K3" s="14"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12"/>
@@ -389,6 +397,7 @@
       <x:c r="I4" s="12"/>
       <x:c r="J4" s="12"/>
       <x:c r="K4" s="14"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12"/>
@@ -402,6 +411,7 @@
       <x:c r="I5" s="12"/>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="14"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12"/>
@@ -415,6 +425,7 @@
       <x:c r="I6" s="12"/>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="14"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12"/>
@@ -428,6 +439,7 @@
       <x:c r="I7" s="12"/>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="14"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12"/>
@@ -441,6 +453,7 @@
       <x:c r="I8" s="12"/>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="14"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12"/>
@@ -454,6 +467,7 @@
       <x:c r="I9" s="12"/>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="14"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12"/>
@@ -467,6 +481,7 @@
       <x:c r="I10" s="12"/>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="14"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12"/>
@@ -480,6 +495,7 @@
       <x:c r="I11" s="12"/>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="14"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="12"/>
@@ -493,6 +509,7 @@
       <x:c r="I12" s="12"/>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="14"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="12"/>
@@ -506,6 +523,7 @@
       <x:c r="I13" s="12"/>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="14"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="12"/>
@@ -519,6 +537,7 @@
       <x:c r="I14" s="12"/>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="12"/>
@@ -532,6 +551,7 @@
       <x:c r="I15" s="12"/>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="14"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="12"/>
@@ -545,6 +565,7 @@
       <x:c r="I16" s="12"/>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="14"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="12"/>
@@ -558,6 +579,7 @@
       <x:c r="I17" s="12"/>
       <x:c r="J17" s="12"/>
       <x:c r="K17" s="14"/>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="12"/>
@@ -571,6 +593,7 @@
       <x:c r="I18" s="12"/>
       <x:c r="J18" s="12"/>
       <x:c r="K18" s="14"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="12"/>
@@ -584,6 +607,7 @@
       <x:c r="I19" s="12"/>
       <x:c r="J19" s="12"/>
       <x:c r="K19" s="14"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="12"/>
@@ -597,6 +621,7 @@
       <x:c r="I20" s="12"/>
       <x:c r="J20" s="12"/>
       <x:c r="K20" s="14"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="12"/>
@@ -610,6 +635,7 @@
       <x:c r="I21" s="12"/>
       <x:c r="J21" s="12"/>
       <x:c r="K21" s="14"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="12"/>
@@ -623,6 +649,7 @@
       <x:c r="I22" s="12"/>
       <x:c r="J22" s="12"/>
       <x:c r="K22" s="14"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="12"/>
@@ -636,6 +663,7 @@
       <x:c r="I23" s="12"/>
       <x:c r="J23" s="12"/>
       <x:c r="K23" s="14"/>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="12"/>
@@ -649,6 +677,7 @@
       <x:c r="I24" s="12"/>
       <x:c r="J24" s="12"/>
       <x:c r="K24" s="14"/>
+      <x:c r="L24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="12"/>
@@ -662,6 +691,7 @@
       <x:c r="I25" s="12"/>
       <x:c r="J25" s="12"/>
       <x:c r="K25" s="14"/>
+      <x:c r="L25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="12"/>
@@ -675,6 +705,7 @@
       <x:c r="I26" s="12"/>
       <x:c r="J26" s="12"/>
       <x:c r="K26" s="14"/>
+      <x:c r="L26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="12"/>
@@ -688,6 +719,7 @@
       <x:c r="I27" s="12"/>
       <x:c r="J27" s="12"/>
       <x:c r="K27" s="14"/>
+      <x:c r="L27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="12"/>
@@ -701,6 +733,7 @@
       <x:c r="I28" s="12"/>
       <x:c r="J28" s="12"/>
       <x:c r="K28" s="14"/>
+      <x:c r="L28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="12"/>
@@ -714,6 +747,7 @@
       <x:c r="I29" s="12"/>
       <x:c r="J29" s="12"/>
       <x:c r="K29" s="14"/>
+      <x:c r="L29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="12"/>
@@ -727,6 +761,7 @@
       <x:c r="I30" s="12"/>
       <x:c r="J30" s="12"/>
       <x:c r="K30" s="14"/>
+      <x:c r="L30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="12"/>
@@ -740,6 +775,7 @@
       <x:c r="I31" s="12"/>
       <x:c r="J31" s="12"/>
       <x:c r="K31" s="14"/>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="12"/>
@@ -753,6 +789,7 @@
       <x:c r="I32" s="12"/>
       <x:c r="J32" s="12"/>
       <x:c r="K32" s="14"/>
+      <x:c r="L32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="12"/>
@@ -766,6 +803,7 @@
       <x:c r="I33" s="12"/>
       <x:c r="J33" s="12"/>
       <x:c r="K33" s="14"/>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="12"/>
@@ -779,6 +817,7 @@
       <x:c r="I34" s="12"/>
       <x:c r="J34" s="12"/>
       <x:c r="K34" s="14"/>
+      <x:c r="L34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="12"/>
@@ -792,6 +831,7 @@
       <x:c r="I35" s="12"/>
       <x:c r="J35" s="12"/>
       <x:c r="K35" s="14"/>
+      <x:c r="L35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="12"/>
@@ -805,6 +845,7 @@
       <x:c r="I36" s="12"/>
       <x:c r="J36" s="12"/>
       <x:c r="K36" s="14"/>
+      <x:c r="L36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="12"/>
@@ -818,6 +859,7 @@
       <x:c r="I37" s="12"/>
       <x:c r="J37" s="12"/>
       <x:c r="K37" s="14"/>
+      <x:c r="L37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="12"/>
@@ -831,6 +873,7 @@
       <x:c r="I38" s="12"/>
       <x:c r="J38" s="12"/>
       <x:c r="K38" s="14"/>
+      <x:c r="L38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="12"/>
@@ -844,6 +887,7 @@
       <x:c r="I39" s="12"/>
       <x:c r="J39" s="12"/>
       <x:c r="K39" s="14"/>
+      <x:c r="L39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="12"/>
@@ -857,6 +901,7 @@
       <x:c r="I40" s="12"/>
       <x:c r="J40" s="12"/>
       <x:c r="K40" s="14"/>
+      <x:c r="L40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="12"/>
@@ -870,6 +915,7 @@
       <x:c r="I41" s="12"/>
       <x:c r="J41" s="12"/>
       <x:c r="K41" s="14"/>
+      <x:c r="L41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="12"/>
@@ -883,6 +929,7 @@
       <x:c r="I42" s="12"/>
       <x:c r="J42" s="12"/>
       <x:c r="K42" s="14"/>
+      <x:c r="L42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="12"/>
@@ -896,6 +943,7 @@
       <x:c r="I43" s="12"/>
       <x:c r="J43" s="12"/>
       <x:c r="K43" s="14"/>
+      <x:c r="L43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="12"/>
@@ -909,6 +957,7 @@
       <x:c r="I44" s="12"/>
       <x:c r="J44" s="12"/>
       <x:c r="K44" s="14"/>
+      <x:c r="L44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="12"/>
@@ -922,6 +971,7 @@
       <x:c r="I45" s="12"/>
       <x:c r="J45" s="12"/>
       <x:c r="K45" s="14"/>
+      <x:c r="L45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="12"/>
@@ -935,6 +985,7 @@
       <x:c r="I46" s="12"/>
       <x:c r="J46" s="12"/>
       <x:c r="K46" s="14"/>
+      <x:c r="L46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="12"/>
@@ -948,6 +999,7 @@
       <x:c r="I47" s="12"/>
       <x:c r="J47" s="12"/>
       <x:c r="K47" s="14"/>
+      <x:c r="L47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="12"/>
@@ -961,6 +1013,7 @@
       <x:c r="I48" s="12"/>
       <x:c r="J48" s="12"/>
       <x:c r="K48" s="14"/>
+      <x:c r="L48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="12"/>
@@ -974,6 +1027,7 @@
       <x:c r="I49" s="12"/>
       <x:c r="J49" s="12"/>
       <x:c r="K49" s="14"/>
+      <x:c r="L49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="12"/>
@@ -987,6 +1041,7 @@
       <x:c r="I50" s="12"/>
       <x:c r="J50" s="12"/>
       <x:c r="K50" s="14"/>
+      <x:c r="L50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="12"/>
@@ -1000,6 +1055,7 @@
       <x:c r="I51" s="12"/>
       <x:c r="J51" s="12"/>
       <x:c r="K51" s="14"/>
+      <x:c r="L51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="12"/>
@@ -1013,6 +1069,7 @@
       <x:c r="I52" s="12"/>
       <x:c r="J52" s="12"/>
       <x:c r="K52" s="14"/>
+      <x:c r="L52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="12"/>
@@ -1026,6 +1083,7 @@
       <x:c r="I53" s="12"/>
       <x:c r="J53" s="12"/>
       <x:c r="K53" s="14"/>
+      <x:c r="L53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="12"/>
@@ -1039,6 +1097,7 @@
       <x:c r="I54" s="12"/>
       <x:c r="J54" s="12"/>
       <x:c r="K54" s="14"/>
+      <x:c r="L54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="12"/>
@@ -1052,6 +1111,7 @@
       <x:c r="I55" s="12"/>
       <x:c r="J55" s="12"/>
       <x:c r="K55" s="14"/>
+      <x:c r="L55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="12"/>
@@ -1065,6 +1125,7 @@
       <x:c r="I56" s="12"/>
       <x:c r="J56" s="12"/>
       <x:c r="K56" s="14"/>
+      <x:c r="L56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="12"/>
@@ -1078,6 +1139,7 @@
       <x:c r="I57" s="12"/>
       <x:c r="J57" s="12"/>
       <x:c r="K57" s="14"/>
+      <x:c r="L57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="12"/>
@@ -1091,6 +1153,7 @@
       <x:c r="I58" s="12"/>
       <x:c r="J58" s="12"/>
       <x:c r="K58" s="14"/>
+      <x:c r="L58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="12"/>
@@ -1104,6 +1167,7 @@
       <x:c r="I59" s="12"/>
       <x:c r="J59" s="12"/>
       <x:c r="K59" s="14"/>
+      <x:c r="L59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="12"/>
@@ -1117,6 +1181,7 @@
       <x:c r="I60" s="12"/>
       <x:c r="J60" s="12"/>
       <x:c r="K60" s="14"/>
+      <x:c r="L60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="12"/>
@@ -1130,6 +1195,7 @@
       <x:c r="I61" s="12"/>
       <x:c r="J61" s="12"/>
       <x:c r="K61" s="14"/>
+      <x:c r="L61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="12"/>
@@ -1143,6 +1209,7 @@
       <x:c r="I62" s="12"/>
       <x:c r="J62" s="12"/>
       <x:c r="K62" s="14"/>
+      <x:c r="L62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="12"/>
@@ -1156,6 +1223,7 @@
       <x:c r="I63" s="12"/>
       <x:c r="J63" s="12"/>
       <x:c r="K63" s="14"/>
+      <x:c r="L63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="12"/>
@@ -1169,6 +1237,7 @@
       <x:c r="I64" s="12"/>
       <x:c r="J64" s="12"/>
       <x:c r="K64" s="14"/>
+      <x:c r="L64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="12"/>
@@ -1182,6 +1251,7 @@
       <x:c r="I65" s="12"/>
       <x:c r="J65" s="12"/>
       <x:c r="K65" s="14"/>
+      <x:c r="L65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="12"/>
@@ -1195,6 +1265,7 @@
       <x:c r="I66" s="12"/>
       <x:c r="J66" s="12"/>
       <x:c r="K66" s="14"/>
+      <x:c r="L66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="12"/>
@@ -1208,6 +1279,7 @@
       <x:c r="I67" s="12"/>
       <x:c r="J67" s="12"/>
       <x:c r="K67" s="14"/>
+      <x:c r="L67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="12"/>
@@ -1221,6 +1293,7 @@
       <x:c r="I68" s="12"/>
       <x:c r="J68" s="12"/>
       <x:c r="K68" s="14"/>
+      <x:c r="L68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="12"/>
@@ -1234,6 +1307,7 @@
       <x:c r="I69" s="12"/>
       <x:c r="J69" s="12"/>
       <x:c r="K69" s="14"/>
+      <x:c r="L69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="12"/>
@@ -1247,6 +1321,7 @@
       <x:c r="I70" s="12"/>
       <x:c r="J70" s="12"/>
       <x:c r="K70" s="14"/>
+      <x:c r="L70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="12"/>
@@ -1260,6 +1335,7 @@
       <x:c r="I71" s="12"/>
       <x:c r="J71" s="12"/>
       <x:c r="K71" s="14"/>
+      <x:c r="L71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="12"/>
@@ -1273,6 +1349,7 @@
       <x:c r="I72" s="12"/>
       <x:c r="J72" s="12"/>
       <x:c r="K72" s="14"/>
+      <x:c r="L72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="12"/>
@@ -1286,6 +1363,7 @@
       <x:c r="I73" s="12"/>
       <x:c r="J73" s="12"/>
       <x:c r="K73" s="14"/>
+      <x:c r="L73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="12"/>
@@ -1299,6 +1377,7 @@
       <x:c r="I74" s="12"/>
       <x:c r="J74" s="12"/>
       <x:c r="K74" s="14"/>
+      <x:c r="L74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="12"/>
@@ -1312,6 +1391,7 @@
       <x:c r="I75" s="12"/>
       <x:c r="J75" s="12"/>
       <x:c r="K75" s="14"/>
+      <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="12"/>
@@ -1325,6 +1405,7 @@
       <x:c r="I76" s="12"/>
       <x:c r="J76" s="12"/>
       <x:c r="K76" s="14"/>
+      <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="12"/>
@@ -1338,6 +1419,7 @@
       <x:c r="I77" s="12"/>
       <x:c r="J77" s="12"/>
       <x:c r="K77" s="14"/>
+      <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="12"/>
@@ -1351,6 +1433,7 @@
       <x:c r="I78" s="12"/>
       <x:c r="J78" s="12"/>
       <x:c r="K78" s="14"/>
+      <x:c r="L78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="12"/>
@@ -1364,6 +1447,7 @@
       <x:c r="I79" s="12"/>
       <x:c r="J79" s="12"/>
       <x:c r="K79" s="14"/>
+      <x:c r="L79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="12"/>
@@ -1377,6 +1461,7 @@
       <x:c r="I80" s="12"/>
       <x:c r="J80" s="12"/>
       <x:c r="K80" s="14"/>
+      <x:c r="L80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="12"/>
@@ -1390,6 +1475,7 @@
       <x:c r="I81" s="12"/>
       <x:c r="J81" s="12"/>
       <x:c r="K81" s="14"/>
+      <x:c r="L81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="12"/>
@@ -1403,6 +1489,7 @@
       <x:c r="I82" s="12"/>
       <x:c r="J82" s="12"/>
       <x:c r="K82" s="14"/>
+      <x:c r="L82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="12"/>
@@ -1416,6 +1503,7 @@
       <x:c r="I83" s="12"/>
       <x:c r="J83" s="12"/>
       <x:c r="K83" s="14"/>
+      <x:c r="L83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="12"/>
@@ -1429,6 +1517,7 @@
       <x:c r="I84" s="12"/>
       <x:c r="J84" s="12"/>
       <x:c r="K84" s="14"/>
+      <x:c r="L84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="12"/>
@@ -1442,6 +1531,7 @@
       <x:c r="I85" s="12"/>
       <x:c r="J85" s="12"/>
       <x:c r="K85" s="14"/>
+      <x:c r="L85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="12"/>
@@ -1455,6 +1545,7 @@
       <x:c r="I86" s="12"/>
       <x:c r="J86" s="12"/>
       <x:c r="K86" s="14"/>
+      <x:c r="L86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="12"/>
@@ -1468,6 +1559,7 @@
       <x:c r="I87" s="12"/>
       <x:c r="J87" s="12"/>
       <x:c r="K87" s="14"/>
+      <x:c r="L87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="12"/>
@@ -1481,6 +1573,7 @@
       <x:c r="I88" s="12"/>
       <x:c r="J88" s="12"/>
       <x:c r="K88" s="14"/>
+      <x:c r="L88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="12"/>
@@ -1494,6 +1587,7 @@
       <x:c r="I89" s="12"/>
       <x:c r="J89" s="12"/>
       <x:c r="K89" s="14"/>
+      <x:c r="L89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="12"/>
@@ -1507,6 +1601,7 @@
       <x:c r="I90" s="12"/>
       <x:c r="J90" s="12"/>
       <x:c r="K90" s="14"/>
+      <x:c r="L90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="12"/>
@@ -1520,6 +1615,7 @@
       <x:c r="I91" s="12"/>
       <x:c r="J91" s="12"/>
       <x:c r="K91" s="14"/>
+      <x:c r="L91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="12"/>
@@ -1533,6 +1629,7 @@
       <x:c r="I92" s="12"/>
       <x:c r="J92" s="12"/>
       <x:c r="K92" s="14"/>
+      <x:c r="L92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="12"/>
@@ -1546,6 +1643,7 @@
       <x:c r="I93" s="12"/>
       <x:c r="J93" s="12"/>
       <x:c r="K93" s="14"/>
+      <x:c r="L93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="12"/>
@@ -1559,6 +1657,7 @@
       <x:c r="I94" s="12"/>
       <x:c r="J94" s="12"/>
       <x:c r="K94" s="14"/>
+      <x:c r="L94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="12"/>
@@ -1572,6 +1671,7 @@
       <x:c r="I95" s="12"/>
       <x:c r="J95" s="12"/>
       <x:c r="K95" s="14"/>
+      <x:c r="L95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="12"/>
@@ -1585,6 +1685,7 @@
       <x:c r="I96" s="12"/>
       <x:c r="J96" s="12"/>
       <x:c r="K96" s="14"/>
+      <x:c r="L96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="12"/>
@@ -1598,6 +1699,7 @@
       <x:c r="I97" s="12"/>
       <x:c r="J97" s="12"/>
       <x:c r="K97" s="14"/>
+      <x:c r="L97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="12"/>
@@ -1611,6 +1713,7 @@
       <x:c r="I98" s="12"/>
       <x:c r="J98" s="12"/>
       <x:c r="K98" s="14"/>
+      <x:c r="L98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="12"/>
@@ -1624,6 +1727,7 @@
       <x:c r="I99" s="12"/>
       <x:c r="J99" s="12"/>
       <x:c r="K99" s="14"/>
+      <x:c r="L99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="12"/>
@@ -1637,6 +1741,7 @@
       <x:c r="I100" s="12"/>
       <x:c r="J100" s="12"/>
       <x:c r="K100" s="14"/>
+      <x:c r="L100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="12"/>
@@ -1650,6 +1755,7 @@
       <x:c r="I101" s="12"/>
       <x:c r="J101" s="12"/>
       <x:c r="K101" s="14"/>
+      <x:c r="L101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="12"/>
@@ -1663,6 +1769,7 @@
       <x:c r="I102" s="12"/>
       <x:c r="J102" s="12"/>
       <x:c r="K102" s="14"/>
+      <x:c r="L102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="12"/>
@@ -1676,6 +1783,7 @@
       <x:c r="I103" s="12"/>
       <x:c r="J103" s="12"/>
       <x:c r="K103" s="14"/>
+      <x:c r="L103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="12"/>
@@ -1689,6 +1797,7 @@
       <x:c r="I104" s="12"/>
       <x:c r="J104" s="12"/>
       <x:c r="K104" s="14"/>
+      <x:c r="L104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="12"/>
@@ -1702,6 +1811,7 @@
       <x:c r="I105" s="12"/>
       <x:c r="J105" s="12"/>
       <x:c r="K105" s="14"/>
+      <x:c r="L105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="12"/>
@@ -1715,6 +1825,7 @@
       <x:c r="I106" s="12"/>
       <x:c r="J106" s="12"/>
       <x:c r="K106" s="14"/>
+      <x:c r="L106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="12"/>
@@ -1728,6 +1839,7 @@
       <x:c r="I107" s="12"/>
       <x:c r="J107" s="12"/>
       <x:c r="K107" s="14"/>
+      <x:c r="L107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="12"/>
@@ -1741,6 +1853,7 @@
       <x:c r="I108" s="12"/>
       <x:c r="J108" s="12"/>
       <x:c r="K108" s="14"/>
+      <x:c r="L108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="12"/>
@@ -1754,6 +1867,7 @@
       <x:c r="I109" s="12"/>
       <x:c r="J109" s="12"/>
       <x:c r="K109" s="14"/>
+      <x:c r="L109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="12"/>
@@ -1767,6 +1881,7 @@
       <x:c r="I110" s="12"/>
       <x:c r="J110" s="12"/>
       <x:c r="K110" s="14"/>
+      <x:c r="L110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="12"/>
@@ -1780,6 +1895,7 @@
       <x:c r="I111" s="12"/>
       <x:c r="J111" s="12"/>
       <x:c r="K111" s="14"/>
+      <x:c r="L111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="12"/>
@@ -1793,6 +1909,7 @@
       <x:c r="I112" s="12"/>
       <x:c r="J112" s="12"/>
       <x:c r="K112" s="14"/>
+      <x:c r="L112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="12"/>
@@ -1806,6 +1923,7 @@
       <x:c r="I113" s="12"/>
       <x:c r="J113" s="12"/>
       <x:c r="K113" s="14"/>
+      <x:c r="L113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="12"/>
@@ -1819,6 +1937,7 @@
       <x:c r="I114" s="12"/>
       <x:c r="J114" s="12"/>
       <x:c r="K114" s="14"/>
+      <x:c r="L114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="12"/>
@@ -1832,6 +1951,7 @@
       <x:c r="I115" s="12"/>
       <x:c r="J115" s="12"/>
       <x:c r="K115" s="14"/>
+      <x:c r="L115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="12"/>
@@ -1845,6 +1965,7 @@
       <x:c r="I116" s="12"/>
       <x:c r="J116" s="12"/>
       <x:c r="K116" s="14"/>
+      <x:c r="L116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="12"/>
@@ -1858,6 +1979,7 @@
       <x:c r="I117" s="12"/>
       <x:c r="J117" s="12"/>
       <x:c r="K117" s="14"/>
+      <x:c r="L117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="12"/>
@@ -1871,6 +1993,7 @@
       <x:c r="I118" s="12"/>
       <x:c r="J118" s="12"/>
       <x:c r="K118" s="14"/>
+      <x:c r="L118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="12"/>
@@ -1884,6 +2007,7 @@
       <x:c r="I119" s="12"/>
       <x:c r="J119" s="12"/>
       <x:c r="K119" s="14"/>
+      <x:c r="L119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="12"/>
@@ -1897,6 +2021,7 @@
       <x:c r="I120" s="12"/>
       <x:c r="J120" s="12"/>
       <x:c r="K120" s="14"/>
+      <x:c r="L120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="12"/>
@@ -1910,6 +2035,7 @@
       <x:c r="I121" s="12"/>
       <x:c r="J121" s="12"/>
       <x:c r="K121" s="14"/>
+      <x:c r="L121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="12"/>
@@ -1923,6 +2049,7 @@
       <x:c r="I122" s="12"/>
       <x:c r="J122" s="12"/>
       <x:c r="K122" s="14"/>
+      <x:c r="L122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="12"/>
@@ -1936,6 +2063,7 @@
       <x:c r="I123" s="12"/>
       <x:c r="J123" s="12"/>
       <x:c r="K123" s="14"/>
+      <x:c r="L123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="12"/>
@@ -1949,6 +2077,7 @@
       <x:c r="I124" s="12"/>
       <x:c r="J124" s="12"/>
       <x:c r="K124" s="14"/>
+      <x:c r="L124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="12"/>
@@ -1962,6 +2091,7 @@
       <x:c r="I125" s="12"/>
       <x:c r="J125" s="12"/>
       <x:c r="K125" s="14"/>
+      <x:c r="L125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="12"/>
@@ -1975,6 +2105,7 @@
       <x:c r="I126" s="12"/>
       <x:c r="J126" s="12"/>
       <x:c r="K126" s="14"/>
+      <x:c r="L126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="12"/>
@@ -1988,6 +2119,7 @@
       <x:c r="I127" s="12"/>
       <x:c r="J127" s="12"/>
       <x:c r="K127" s="14"/>
+      <x:c r="L127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="12"/>
@@ -2001,6 +2133,7 @@
       <x:c r="I128" s="12"/>
       <x:c r="J128" s="12"/>
       <x:c r="K128" s="14"/>
+      <x:c r="L128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="12"/>
@@ -2014,6 +2147,7 @@
       <x:c r="I129" s="12"/>
       <x:c r="J129" s="12"/>
       <x:c r="K129" s="14"/>
+      <x:c r="L129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="12"/>
@@ -2027,6 +2161,7 @@
       <x:c r="I130" s="12"/>
       <x:c r="J130" s="12"/>
       <x:c r="K130" s="14"/>
+      <x:c r="L130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="12"/>
@@ -2040,6 +2175,7 @@
       <x:c r="I131" s="12"/>
       <x:c r="J131" s="12"/>
       <x:c r="K131" s="14"/>
+      <x:c r="L131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="12"/>
@@ -2053,6 +2189,7 @@
       <x:c r="I132" s="12"/>
       <x:c r="J132" s="12"/>
       <x:c r="K132" s="14"/>
+      <x:c r="L132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="12"/>
@@ -2066,6 +2203,7 @@
       <x:c r="I133" s="12"/>
       <x:c r="J133" s="12"/>
       <x:c r="K133" s="14"/>
+      <x:c r="L133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="12"/>
@@ -2079,6 +2217,7 @@
       <x:c r="I134" s="12"/>
       <x:c r="J134" s="12"/>
       <x:c r="K134" s="14"/>
+      <x:c r="L134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="12"/>
@@ -2092,6 +2231,7 @@
       <x:c r="I135" s="12"/>
       <x:c r="J135" s="12"/>
       <x:c r="K135" s="14"/>
+      <x:c r="L135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="12"/>
@@ -2105,6 +2245,7 @@
       <x:c r="I136" s="12"/>
       <x:c r="J136" s="12"/>
       <x:c r="K136" s="14"/>
+      <x:c r="L136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="12"/>
@@ -2118,6 +2259,7 @@
       <x:c r="I137" s="12"/>
       <x:c r="J137" s="12"/>
       <x:c r="K137" s="14"/>
+      <x:c r="L137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="12"/>
@@ -2131,6 +2273,7 @@
       <x:c r="I138" s="12"/>
       <x:c r="J138" s="12"/>
       <x:c r="K138" s="14"/>
+      <x:c r="L138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="12"/>
@@ -2144,6 +2287,7 @@
       <x:c r="I139" s="12"/>
       <x:c r="J139" s="12"/>
       <x:c r="K139" s="14"/>
+      <x:c r="L139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="12"/>
@@ -2157,6 +2301,7 @@
       <x:c r="I140" s="12"/>
       <x:c r="J140" s="12"/>
       <x:c r="K140" s="14"/>
+      <x:c r="L140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="12"/>
@@ -2170,6 +2315,7 @@
       <x:c r="I141" s="12"/>
       <x:c r="J141" s="12"/>
       <x:c r="K141" s="14"/>
+      <x:c r="L141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="12"/>
@@ -2183,6 +2329,7 @@
       <x:c r="I142" s="12"/>
       <x:c r="J142" s="12"/>
       <x:c r="K142" s="14"/>
+      <x:c r="L142"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="12"/>
@@ -2196,6 +2343,7 @@
       <x:c r="I143" s="12"/>
       <x:c r="J143" s="12"/>
       <x:c r="K143" s="14"/>
+      <x:c r="L143"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="12"/>
@@ -2209,6 +2357,7 @@
       <x:c r="I144" s="12"/>
       <x:c r="J144" s="12"/>
       <x:c r="K144" s="14"/>
+      <x:c r="L144"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="12"/>
@@ -2222,6 +2371,7 @@
       <x:c r="I145" s="12"/>
       <x:c r="J145" s="12"/>
       <x:c r="K145" s="14"/>
+      <x:c r="L145"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="12"/>
@@ -2235,6 +2385,7 @@
       <x:c r="I146" s="12"/>
       <x:c r="J146" s="12"/>
       <x:c r="K146" s="14"/>
+      <x:c r="L146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="12"/>
@@ -2248,6 +2399,7 @@
       <x:c r="I147" s="12"/>
       <x:c r="J147" s="12"/>
       <x:c r="K147" s="14"/>
+      <x:c r="L147"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="12"/>
@@ -2261,6 +2413,7 @@
       <x:c r="I148" s="12"/>
       <x:c r="J148" s="12"/>
       <x:c r="K148" s="14"/>
+      <x:c r="L148"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="12"/>
@@ -2274,6 +2427,7 @@
       <x:c r="I149" s="12"/>
       <x:c r="J149" s="12"/>
       <x:c r="K149" s="14"/>
+      <x:c r="L149"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="12"/>
@@ -2287,6 +2441,7 @@
       <x:c r="I150" s="12"/>
       <x:c r="J150" s="12"/>
       <x:c r="K150" s="14"/>
+      <x:c r="L150"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="12"/>
@@ -2300,6 +2455,7 @@
       <x:c r="I151" s="12"/>
       <x:c r="J151" s="12"/>
       <x:c r="K151" s="14"/>
+      <x:c r="L151"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="12"/>
@@ -2313,6 +2469,7 @@
       <x:c r="I152" s="12"/>
       <x:c r="J152" s="12"/>
       <x:c r="K152" s="14"/>
+      <x:c r="L152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="12"/>
@@ -2326,6 +2483,7 @@
       <x:c r="I153" s="12"/>
       <x:c r="J153" s="12"/>
       <x:c r="K153" s="14"/>
+      <x:c r="L153"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="12"/>
@@ -2339,6 +2497,7 @@
       <x:c r="I154" s="12"/>
       <x:c r="J154" s="12"/>
       <x:c r="K154" s="14"/>
+      <x:c r="L154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="12"/>
@@ -2352,6 +2511,7 @@
       <x:c r="I155" s="12"/>
       <x:c r="J155" s="12"/>
       <x:c r="K155" s="14"/>
+      <x:c r="L155"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="12"/>
@@ -2365,6 +2525,7 @@
       <x:c r="I156" s="12"/>
       <x:c r="J156" s="12"/>
       <x:c r="K156" s="14"/>
+      <x:c r="L156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="12"/>
@@ -2378,6 +2539,7 @@
       <x:c r="I157" s="12"/>
       <x:c r="J157" s="12"/>
       <x:c r="K157" s="14"/>
+      <x:c r="L157"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="12"/>
@@ -2391,6 +2553,7 @@
       <x:c r="I158" s="12"/>
       <x:c r="J158" s="12"/>
       <x:c r="K158" s="14"/>
+      <x:c r="L158"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="12"/>
@@ -2404,6 +2567,7 @@
       <x:c r="I159" s="12"/>
       <x:c r="J159" s="12"/>
       <x:c r="K159" s="14"/>
+      <x:c r="L159"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="12"/>
@@ -2417,6 +2581,7 @@
       <x:c r="I160" s="12"/>
       <x:c r="J160" s="12"/>
       <x:c r="K160" s="14"/>
+      <x:c r="L160"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="12"/>
@@ -2430,6 +2595,7 @@
       <x:c r="I161" s="12"/>
       <x:c r="J161" s="12"/>
       <x:c r="K161" s="14"/>
+      <x:c r="L161"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="12"/>
@@ -2443,6 +2609,7 @@
       <x:c r="I162" s="12"/>
       <x:c r="J162" s="12"/>
       <x:c r="K162" s="14"/>
+      <x:c r="L162"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="12"/>
@@ -2456,6 +2623,7 @@
       <x:c r="I163" s="12"/>
       <x:c r="J163" s="12"/>
       <x:c r="K163" s="14"/>
+      <x:c r="L163"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="12"/>
@@ -2469,6 +2637,7 @@
       <x:c r="I164" s="12"/>
       <x:c r="J164" s="12"/>
       <x:c r="K164" s="14"/>
+      <x:c r="L164"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="12"/>
@@ -2482,6 +2651,7 @@
       <x:c r="I165" s="12"/>
       <x:c r="J165" s="12"/>
       <x:c r="K165" s="14"/>
+      <x:c r="L165"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="12"/>
@@ -2495,6 +2665,7 @@
       <x:c r="I166" s="12"/>
       <x:c r="J166" s="12"/>
       <x:c r="K166" s="14"/>
+      <x:c r="L166"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="12"/>
@@ -2508,6 +2679,7 @@
       <x:c r="I167" s="12"/>
       <x:c r="J167" s="12"/>
       <x:c r="K167" s="14"/>
+      <x:c r="L167"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="12"/>
@@ -2521,6 +2693,7 @@
       <x:c r="I168" s="12"/>
       <x:c r="J168" s="12"/>
       <x:c r="K168" s="14"/>
+      <x:c r="L168"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="12"/>
@@ -2534,6 +2707,7 @@
       <x:c r="I169" s="12"/>
       <x:c r="J169" s="12"/>
       <x:c r="K169" s="14"/>
+      <x:c r="L169"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="12"/>
@@ -2547,6 +2721,7 @@
       <x:c r="I170" s="12"/>
       <x:c r="J170" s="12"/>
       <x:c r="K170" s="14"/>
+      <x:c r="L170"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="12"/>
@@ -2560,6 +2735,7 @@
       <x:c r="I171" s="12"/>
       <x:c r="J171" s="12"/>
       <x:c r="K171" s="14"/>
+      <x:c r="L171"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="12"/>
@@ -2573,6 +2749,7 @@
       <x:c r="I172" s="12"/>
       <x:c r="J172" s="12"/>
       <x:c r="K172" s="14"/>
+      <x:c r="L172"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="12"/>
@@ -2586,6 +2763,7 @@
       <x:c r="I173" s="12"/>
       <x:c r="J173" s="12"/>
       <x:c r="K173" s="14"/>
+      <x:c r="L173"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="12"/>
@@ -2599,6 +2777,7 @@
       <x:c r="I174" s="12"/>
       <x:c r="J174" s="12"/>
       <x:c r="K174" s="14"/>
+      <x:c r="L174"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="12"/>
@@ -2612,6 +2791,7 @@
       <x:c r="I175" s="12"/>
       <x:c r="J175" s="12"/>
       <x:c r="K175" s="14"/>
+      <x:c r="L175"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="12"/>
@@ -2625,6 +2805,7 @@
       <x:c r="I176" s="12"/>
       <x:c r="J176" s="12"/>
       <x:c r="K176" s="14"/>
+      <x:c r="L176"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="12"/>
@@ -2638,6 +2819,7 @@
       <x:c r="I177" s="12"/>
       <x:c r="J177" s="12"/>
       <x:c r="K177" s="14"/>
+      <x:c r="L177"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="12"/>
@@ -2651,6 +2833,7 @@
       <x:c r="I178" s="12"/>
       <x:c r="J178" s="12"/>
       <x:c r="K178" s="14"/>
+      <x:c r="L178"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="12"/>
@@ -2664,6 +2847,7 @@
       <x:c r="I179" s="12"/>
       <x:c r="J179" s="12"/>
       <x:c r="K179" s="14"/>
+      <x:c r="L179"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="12"/>
@@ -2677,6 +2861,7 @@
       <x:c r="I180" s="12"/>
       <x:c r="J180" s="12"/>
       <x:c r="K180" s="14"/>
+      <x:c r="L180"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="12"/>
@@ -2690,6 +2875,7 @@
       <x:c r="I181" s="12"/>
       <x:c r="J181" s="12"/>
       <x:c r="K181" s="14"/>
+      <x:c r="L181"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="12"/>
@@ -2703,6 +2889,7 @@
       <x:c r="I182" s="12"/>
       <x:c r="J182" s="12"/>
       <x:c r="K182" s="14"/>
+      <x:c r="L182"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="12"/>
@@ -2716,6 +2903,7 @@
       <x:c r="I183" s="12"/>
       <x:c r="J183" s="12"/>
       <x:c r="K183" s="14"/>
+      <x:c r="L183"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="12"/>
@@ -2729,6 +2917,7 @@
       <x:c r="I184" s="12"/>
       <x:c r="J184" s="12"/>
       <x:c r="K184" s="14"/>
+      <x:c r="L184"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="12"/>
@@ -2742,6 +2931,7 @@
       <x:c r="I185" s="12"/>
       <x:c r="J185" s="12"/>
       <x:c r="K185" s="14"/>
+      <x:c r="L185"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="12"/>
@@ -2755,6 +2945,7 @@
       <x:c r="I186" s="12"/>
       <x:c r="J186" s="12"/>
       <x:c r="K186" s="14"/>
+      <x:c r="L186"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="12"/>
@@ -2768,6 +2959,7 @@
       <x:c r="I187" s="12"/>
       <x:c r="J187" s="12"/>
       <x:c r="K187" s="14"/>
+      <x:c r="L187"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="12"/>
@@ -2781,6 +2973,7 @@
       <x:c r="I188" s="12"/>
       <x:c r="J188" s="12"/>
       <x:c r="K188" s="14"/>
+      <x:c r="L188"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="12"/>
@@ -2794,6 +2987,7 @@
       <x:c r="I189" s="12"/>
       <x:c r="J189" s="12"/>
       <x:c r="K189" s="14"/>
+      <x:c r="L189"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="12"/>
@@ -2807,6 +3001,7 @@
       <x:c r="I190" s="12"/>
       <x:c r="J190" s="12"/>
       <x:c r="K190" s="14"/>
+      <x:c r="L190"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="12"/>
@@ -2820,6 +3015,7 @@
       <x:c r="I191" s="12"/>
       <x:c r="J191" s="12"/>
       <x:c r="K191" s="14"/>
+      <x:c r="L191"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="12"/>
@@ -2833,6 +3029,7 @@
       <x:c r="I192" s="12"/>
       <x:c r="J192" s="12"/>
       <x:c r="K192" s="14"/>
+      <x:c r="L192"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="12"/>
@@ -2846,6 +3043,7 @@
       <x:c r="I193" s="12"/>
       <x:c r="J193" s="12"/>
       <x:c r="K193" s="14"/>
+      <x:c r="L193"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="12"/>
@@ -2859,6 +3057,7 @@
       <x:c r="I194" s="12"/>
       <x:c r="J194" s="12"/>
       <x:c r="K194" s="14"/>
+      <x:c r="L194"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="12"/>
@@ -2872,6 +3071,7 @@
       <x:c r="I195" s="12"/>
       <x:c r="J195" s="12"/>
       <x:c r="K195" s="14"/>
+      <x:c r="L195"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="12"/>
@@ -2885,6 +3085,7 @@
       <x:c r="I196" s="12"/>
       <x:c r="J196" s="12"/>
       <x:c r="K196" s="14"/>
+      <x:c r="L196"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="12"/>
@@ -2898,6 +3099,7 @@
       <x:c r="I197" s="12"/>
       <x:c r="J197" s="12"/>
       <x:c r="K197" s="14"/>
+      <x:c r="L197"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="12"/>
@@ -2911,6 +3113,7 @@
       <x:c r="I198" s="12"/>
       <x:c r="J198" s="12"/>
       <x:c r="K198" s="14"/>
+      <x:c r="L198"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="12"/>
@@ -2924,6 +3127,7 @@
       <x:c r="I199" s="12"/>
       <x:c r="J199" s="12"/>
       <x:c r="K199" s="14"/>
+      <x:c r="L199"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="12"/>
@@ -2937,6 +3141,7 @@
       <x:c r="I200" s="12"/>
       <x:c r="J200" s="12"/>
       <x:c r="K200" s="14"/>
+      <x:c r="L200"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="12"/>
@@ -13413,12 +13618,20 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="27"/>
-      <x:c r="B6" s="12"/>
+      <x:c r="A6" s="27" t="str">
+        <x:v>Kilometraje</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>KM_ACTUAL es el odómetro vigente. PROXIMA_MANTENCION_KM sugiere KM_ACTUAL + 10.000, pero puede definirse antes o después.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="27"/>
-      <x:c r="B7" s="12"/>
+      <x:c r="A7" s="27" t="str">
+        <x:v>Prevención</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>E-fleet inicia avisos 1.000 km antes del objetivo; a 500 km exige programar si aún no existe mantención activa.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="27"/>
